--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -711,7 +711,11 @@
 Senna earned it walking dogs in the neighborhood. "It's a great way to make some money," Senna says.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>em1-02-l1r7-senna-coins-r3.webp</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
@@ -878,7 +882,11 @@
 He decides to start his own business: a lemonade stand!</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>em1-03-l1r11-lars-lemonade-r3.webp</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -1262,7 +1262,11 @@
 Mom says she'll help, but Lars has to pay for part of it himself. Pocket money won't get him there, so Lars makes a plan: a lemonade stand!</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>em1-04-l2r20-lars-mom-bike-note-r3.webp</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -2934,7 +2934,11 @@
 "I could design the sign for your stand," she says.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l6-r1.webp</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="inlineStr">
@@ -3414,7 +3418,11 @@
 His startup envelope stays at home. Today's money is just for the mall.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l7-r1.webp</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="inlineStr">

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -1300,7 +1300,11 @@
 Mom agrees, as long as the stand goes by their front gate, where she can see him.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-stand-set-r1.webp</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
@@ -1548,7 +1552,11 @@
 Every time he gets money, some goes in. Next time something breaks, he'll be ready.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-emergencies-jar-r1.webp</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="inlineStr">
@@ -1717,7 +1725,11 @@
 "Before you buy something, ask if you really want or need it," says his school friend Mason. "That's how I've saved so much."</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lars-mason-r1.webp</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
@@ -2108,7 +2120,11 @@
           <t>Lars grabs an envelope to keep his stand money separate. He writes 'Startup money needed: $15' on the front.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lars-thinking-r1.webp</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="inlineStr">
@@ -2142,7 +2158,11 @@
 He pictures his stand by the front gate, with a bright sign and a jug of lemonade.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-stand-set-r1.webp</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="inlineStr">
@@ -2900,7 +2920,11 @@
 His startup money stayed at $10, and he still has $3 spare.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l6-r1.webp</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="inlineStr">
@@ -2934,11 +2958,7 @@
 "I could design the sign for your stand," she says.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>beat-ex-m1-l6-r1.webp</t>
-        </is>
-      </c>
+      <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="inlineStr">
@@ -3009,7 +3029,11 @@
 Mom told the neighbors, and lots of them want to buy lemonade!</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l7-r1.webp</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="inlineStr">
@@ -3384,7 +3408,11 @@
 "Deals like that used to get me every time," Lars laughs.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-slushie-r1.webp</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="inlineStr">
@@ -3420,7 +3448,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>beat-ex-m1-l7-r1.webp</t>
+          <t>prop-ex-m1-bike-bubble-r1.webp</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -3456,7 +3484,11 @@
 What he does with his money today is up to you!</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l8-r2.webp</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="inlineStr">
@@ -4664,7 +4696,11 @@
 On Saturday, his stand opens by the front gate.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l9-r1.webp</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="inlineStr">
@@ -4697,7 +4733,11 @@
           <t>He's one step closer to his mountain bike!</t>
         </is>
       </c>
-      <c r="F102" s="2" t="n"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lars-cheering-bike-r1.webp</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="inlineStr">

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>prop-ex-m1-slushie-r1.webp</t>
+          <t>prop-ex-m1-slushie-r2.webp</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29400" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explorer M1 Screens" sheetId="1" state="visible" r:id="rId1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="146" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -525,76 +525,67 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Meet Lars. He's 11, loves riding his bike and he lives with Mom, Dad and his big brother Senna. Lars spends every dollar the minute it lands in his hands. Follow along with Lars as he moves from being broke, to earning and having money to buy what he really wants. You'll learn the same moves right alongside him.
+Are you ready? Let's go!</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Module intro and first screen of the Academy, before L1 S1. First voiced beat in L1, so it carries the 'Created with Grok' credit.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Lars at home, grinning beside his bike, with Mom, Dad and his big brother Senna in the background, coins and a bill slipping through his fingers.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>word-drop</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Lars just got $20 for his birthday! He runs to the store, but his brain tricks him into thinking cash must be ______ right away!</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>OPTIONS: spent | saved | hidden
 CORRECT: spent</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Lars buys a giant bag of sour worms and a fidget spinner. He's super happy, but ten minutes later...</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>lars-sitting-512.webp</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>CHOICE A: 🍬 ...the candy is gone and the toy feels boring.
-CHOICE B: 💵 ...his $20 magically comes back.
-CORRECT: A</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -615,25 +606,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Lars buys a giant bag of sour worms and a fidget spinner. He's super happy, but ten minutes later...</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>lars-sitting-512.webp</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CHOICE A: 🍬 ...the candy is gone and the toy feels boring.
+CHOICE B: 💵 ...his $20 magically comes back.
+CORRECT: A</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>tap-reveal</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Lars's money is gone, and the fun lasted only 10 minutes. Tap each item to see if it's short fun or fun that lasts!</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>ITEMS:
 SHORT: 🍬 Sour worms
@@ -642,43 +676,43 @@
 LONG: 🛹 Skateboard</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>bucket-sort</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Your turn! Drag each item into the right bucket. How long will the fun really last?</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>ITEMS:
 SHORT: 🍕 Pizza slice
@@ -687,175 +721,132 @@
 LONG: 🃏 Deck of cards</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Lars's birthday money is gone. At home, he watches his big brother Senna count his money.
 Senna earned it walking dogs in the neighborhood. "It's a great way to make some money," Senna says.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>em1-02-l1r7-senna-coins-r3.webp</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>After L1 S4</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Lars sitting on the edge of a bed, watching his big brother Senna count dog-walking money into a jar at home.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Next day, Lars gets his $5 pocket money. Then his tablet flashes: 💥 RARE SKIN DEAL! ONLY 1 MINUTE LEFT! 💥 Why is the game rushing him?</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>lars-deciding-512.webp</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🧠 To trick his brain into buying fast.
 CHOICE B: ❤️ Because the game makers love him.
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Don't fall for the flashing countdown! Try again!</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>hold-to-fill</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Help Lars by giving him a 'buy freeze', so his brain has time to think.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>lars-hands-on-hips-512.webp</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>HOLD: ❄️ HOLD TO FREEZE ❄️
 FROZEN: ❄️ FROZEN ❄️
 SUCCESS: Frozen! Now Lars has time to think.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The freeze worked! The next morning, Lars doesn't even want that skin anymore. What did the freeze help him do with his $5?</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>lars-celebrating-512.webp</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>CHOICE A: 💰 Keep his $5 safe
-CHOICE B: 🎮 Buy the skin even faster
-CORRECT: A</t>
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
@@ -871,67 +862,73 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The freeze worked! The next morning, Lars doesn't even want that skin anymore. What did the freeze help him do with his $5?</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>lars-celebrating-512.webp</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>CHOICE A: 💰 Keep his $5 safe
+CHOICE B: 🎮 Buy the skin even faster
+CORRECT: A</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Lars kept his $5 safe today. That night, he thinks about Senna's dog walking.
 He decides to start his own business: a lemonade stand!</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>em1-03-l1r11-lars-lemonade-r3.webp</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Lars at his desk at night, drawing a lemonade stand in his notebook, a $5 bill beside him.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>completion</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>medal-skill1-bronze.webp</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>MEDAL: bronze</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Lars at his desk at night, drawing a lemonade stand in his notebook, a $5 bill beside him.</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -942,32 +939,28 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>true-false</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Lars promised Senna a $10 phone case for his birthday on Saturday. Lars only has the $5 he kept safe. True or false: he can buy the case now.</t>
-        </is>
-      </c>
+          <t>completion</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>lars-senna-chatting.webp</t>
+          <t>medal-skill1-bronze.webp</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>CORRECT: False</t>
+          <t>MEDAL: bronze</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -975,7 +968,7 @@
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
     </row>
-    <row r="13" ht="80" customHeight="1">
+    <row r="13" ht="64" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -983,30 +976,109 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Senna's birthday is on Saturday, and Lars has a plan.
+He's going to get Senna the cool phone case from the store window. There's just one problem...</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lars-thinking-r1.webp</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>L2 opener, before L2 S1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Lars outside a store window, pointing at a phone case on display, his wallet in his other hand.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>true-false</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Lars promised Senna a $10 phone case for his birthday on Saturday. Lars only has the $5 he kept safe. True or false: he can buy the case now.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>lars-senna-chatting.webp</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT: False</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="112" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>bucket-sort</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Lars spent his birthday money on things he wanted, and saved nothing for things he needs. Help him sort each item.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>ITEMS:
 NEED: 📱 Phone case (birthday present)
@@ -1015,43 +1087,43 @@
 WANT: 🎮 New game skin</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="112" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Needs come before wants. In each round, tap the one Lars should buy first.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>ROUNDS:
 A: 📱 A new case for his own phone (his is fine) | B: 🎁 The phone case he promised Senna | CORRECT: B
@@ -1059,43 +1131,43 @@
 A: 🍱 Pay for lunch for all his friends | B: 🥪 Buy lunch at school for himself | CORRECT: B</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Lars writes a list of things he might buy next. Which ones does he really need? Select all that apply.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>lars-sitting-512.webp</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🎒 A new schoolbag
 CHOICE B: 🥤 Fancy smoothie
@@ -1103,87 +1175,125 @@
 CORRECT: A+C</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Lars asks Mom if he can earn some extra money before Saturday.
+Mom hands him a chore list. "Get these done by Friday, and they're worth $10."</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lars-thinking-r1.webp</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>After L2 S4</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Lars and Mom in the kitchen, Mom handing Lars a chore list, Lars looking keen.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>allocation-slider</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>On Friday, Lars earns $10 helping Mom with chores. Now he has $15. The phone case costs $10.
 Slide to keep at least $10 for the gift.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>lars-hands-on-hips-512.webp</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>TOTAL: 15
 KEEP: 10
 ITEM: 🎁 Phone case</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>rank-order</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Lars has $5 left after saving the gift money. At the store, a sign says 2-FOR-1 JUICE! Rank his choices from best to worst.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>ITEMS: 🫙 Keep his $5 for things he needs.
 ITEMS: 🧃 Buy the deal while it lasts.
@@ -1191,164 +1301,51 @@
 ORDER: keep, buy, borrow</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Not quite! Keeping his $5 comes first. Try again!</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="102" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>drag-to-target</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>It's Saturday, Senna's birthday, and the party is about to start. Drag the gift to Senna so Lars can keep his promise.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>lars-senna-sidebyside.webp</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>SOURCE: concept-gift-box
 TARGET: senna-celebrating
 SUCCESS: Promise kept! Happy birthday, Senna! 🎉</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="102" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Scenario Beat</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Senna loves his new phone case. That night, Lars tells Mom his big dream: swapping his old bike for a better mountain bike.
-Mom says she'll help, but Lars has to pay for part of it himself. Pocket money won't get him there, so Lars makes a plan: a lemonade stand!</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>em1-04-l2r20-lars-mom-bike-note-r3.webp</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>After L2 S7 (beat image 1 of 2)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Lars and Mom talking at the kitchen table in the evening, Lars excited, a picture of a mountain bike in his mind.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="85" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Scenario Beat</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>First he needs a jug, paper cups, lemons and sugar. That costs money too, so he decides to save for it.
-Mom agrees, as long as the stand goes by their front gate, where she can see him.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>prop-ex-m1-stand-set-r1.webp</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>After L2 S7 (beat image 2 of 2)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Lars writing his startup list (jug, cups, lemons, sugar) while Mom reads over his shoulder, smiling.</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>completion</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>medal-skill2-bronze.webp</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>MEDAL: bronze</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
@@ -1356,7 +1353,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
     </row>
-    <row r="22" ht="80" customHeight="1">
+    <row r="22" ht="85" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1364,30 +1361,181 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Senna loves his new phone case. That night, Lars tells Mom his big dream: swapping his old bike for a better mountain bike.
+Mom says she'll help, but Lars has to pay for part of it himself. Pocket money won't get him there, so Lars makes a plan: a lemonade stand!</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>em1-04-l2r20-lars-mom-bike-note-r3.webp</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>After L2 S7 (beat image 1 of 2)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Lars and Mom talking at the kitchen table in the evening, Lars excited, a picture of a mountain bike in his mind.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>First he needs a jug, paper cups, lemons and sugar. That costs money too, so he decides to save for it.
+Mom agrees, as long as the stand goes by their front gate, where she can see him.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-stand-set-r1.webp</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>After L2 S7 (beat image 2 of 2)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Lars writing his startup list (jug, cups, lemons, sugar) while Mom reads over his shoulder, smiling.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>completion</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>medal-skill2-bronze.webp</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>MEDAL: bronze</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Saving for the stand sounds easy. But his friends keep heading to the corner store, and the weeks fly by.
+Then one afternoon, Lars borrows Senna's headphones...</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l3-r1.webp</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>L3 opener, before L3 S1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Lars on the couch wearing his big brother Senna's headphones, a snack wrapper beside him.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="85" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Over the next few weeks, Lars spends every dollar on fun stuff and forgets to save. Then he breaks Senna's headphones by accident. What's the real problem?</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>lars-senna-chatting.webp</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 💸 Lars has no money for a new pair.
 CHOICE B: 🩹 Lars tapes them up and makes them worse.
@@ -1395,43 +1543,43 @@
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="85" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>bucket-sort</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Where did his money go? New headphones cost $20, but Lars's wallet is empty. Drag everything Lars bought into the Spent bucket.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>TOTAL: $20
 ITEMS:
@@ -1440,43 +1588,43 @@
 SPENT: 🍫 Snacks - $5</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-    </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>link-match</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Senna isn't upset for long, but Lars hates this feeling. Senna says keeping Cash for Emergencies gives you choices. Match each event to what you could do.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>PAIRS:
 I broke my brother's headphones = I can replace them
@@ -1484,43 +1632,43 @@
 There's a sale at the game store = I can buy my favorite game now</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>rank-order</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Senna helps Lars make a plan, so he's never caught out again. Put the plan in order, first to last.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>ITEMS: 💵 First, Lars gets his pocket money.
 ITEMS: 🫙 Next, some goes in his Emergencies jar.
@@ -1528,81 +1676,81 @@
 ORDER: pocket, jar, fun</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="80" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Lars finds an old jam jar and writes 'Emergencies' on the lid. It's only a jar, but it's a start.
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Lars finds an old jam jar and writes 'Emergencies' on the lid to save for when things go wrong. It's only a jar, but it's a start.
 Every time he gets money, some goes in. Next time something breaks, he'll be ready.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>prop-ex-m1-emergencies-jar-r1.webp</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>After L3 S4</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Lars at his desk, writing 'Emergencies' on the lid of an old jam jar, a few coins beside it.</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="K30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>A few weeks later, Lars has saved $20, just enough for Senna's new headphones. Then he sees a $5 toy car. "I'll buy it now and save more next week," he thinks. What should he do?</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>lars-deciding-512.webp</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🚗 Buy the toy car and save $5 more next week.
 CHOICE B: 🎧 Buy Senna's new headphones first.
@@ -1610,89 +1758,89 @@
 CORRECT: B</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>That's a trap! Stick to the plan, so there's no stress later. Try again!</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>word-drop</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Lars thinks: "Because I didn't ______ it all, I had cash to ______ Senna's headphones right away."</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>lars-celebrating-512.webp</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>OPTIONS: 💸 spend | 🫙 save | 🔧 replace | 🗑️ throw away
 CORRECT: 💸 spend, 🔧 replace</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="80" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Lars could replace the headphones because he kept some cash aside. Which are good things about keeping some money? Pick all that apply.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🔧 If something breaks, I can replace it.
 CHOICE B: 🎯 I can save for something big.
@@ -1701,118 +1849,156 @@
 CORRECT: A+B+C</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>The headphones are replaced, but Lars's startup money is still $0.
 "Before you buy something, ask if you really want or need it," says his school friend Mason. "That's how I've saved so much."</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>prop-ex-m1-lars-mason-r1.webp</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>After L3 S7</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Lars and his school friend Mason eating lunch in the school yard, Mason giving advice with a calm shrug.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="K34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>completion</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>medal-skill3-bronze.webp</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>MEDAL: bronze</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="64" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>At lunch, everyone's phones are buzzing. A new skin has dropped, and a countdown is ticking.
+Lars remembers Mason's words. His startup money is still $0.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l4-r1.webp</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>L4 opener, before L4 S1</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Lars and Mason at lunch in the school yard, friends around them staring at their phones.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="112" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Lars's friends are all buying a game skin before the timer runs out. Mason sees Lars holding off. What is Lars really doing by waiting?</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>lars-mason-sidebyside.webp</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🐢 Lars is just slow at clicking.
 CHOICE B: 🫙 Lars has run out of money.
@@ -1820,43 +2006,43 @@
 CORRECT: C</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="112" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="112" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>rank-order</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>The next day, Mason asks why Lars waited. "First I saw the countdown. Then I remembered my buy freeze," Lars says. Put Lars's story in order, first to last.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>ITEMS: ⏰ Lars sees the countdown.
 ITEMS: 🧠 He remembers his buy freeze.
@@ -1865,43 +2051,43 @@
 ORDER: countdown, freeze, half, glad</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="112" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+    </row>
+    <row r="39" ht="96" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Lars's head is buzzing about the skin. In each round, which thought helps him stop and think?</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>ROUNDS:
 A: ⏰ It ends soon. I have to buy it now! | B: 💰 I can wait and maybe get it cheaper. | CORRECT: B
@@ -1909,43 +2095,80 @@
 A: 👥 Everyone has it. I can't be left out! | B: 💬 I'll ask my friends if it's any good. | CORRECT: B</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="96" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>After school, Lars walks home past the shops. Every window seems to be shouting at him.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lars-thinking-r1.webp</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>After L4 S3</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Lars walking past a row of shop windows full of bright sale signs.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n"/>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>A bright sign outside a store grabs Lars's eye. Which parts of the sign are trying to make him rush? Pick all that apply.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>fishing-rod-sign.webp</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: DON'T MISS OUT!
 CHOICE B: ONLY 2 LEFT!
@@ -1955,51 +2178,51 @@
 CORRECT: A+B+C</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Hold up! That's just sign info, not a rush trick. Try again!</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Options match the existing sign art (fishing-rod-sign.webp).</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="80" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+    </row>
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Lars gets a limited-time offer for extra lives in his game. He remembers the skin that dropped to half price, so he pauses. What should he ask himself? Pick all that apply.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: Do I really need this?
 CHOICE B: Do I want it now, or is something rushing me?
@@ -2008,43 +2231,43 @@
 CORRECT: A+B+C</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-    </row>
-    <row r="37" ht="80" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+    </row>
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>drag-to-target</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Lars keeps his money instead of buying extra lives. Drag his money from Spend Now to Save for Later.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>lars-celebrating-512.webp</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>SOURCE: 🛒 Spend Now
 TARGET: 🐷 Save for Later
@@ -2053,43 +2276,43 @@
 SUCCESS: Money saved!</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="80" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>savings-goal</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Lars's startup money started at $0. He put the money from three things he skipped into his envelope. Drag each one into the box to watch his startup money climb.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>TARGET: 10
 LABEL: Startup money
@@ -2097,285 +2320,323 @@
 ITEMS: 🍫 Snacks at school ($2) 🎮 Extra lives bundle ($3) ✨ Glow sticks ($5)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Lars grabs an envelope to keep his stand money separate. He writes 'Startup money needed: $15' on the front.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>prop-ex-m1-lars-thinking-r1.webp</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>After L4 S7 (beat image 1 of 2)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Lars at his desk writing 'Startup money needed: $15' on an envelope, coins stacked beside it.</t>
         </is>
       </c>
-      <c r="K39" s="2" t="n"/>
-    </row>
-    <row r="40" ht="64" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="K45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>He tucks the envelope away. $10 saved, $5 to go.
 He pictures his stand by the front gate, with a bright sign and a jug of lemonade.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>prop-ex-m1-stand-set-r1.webp</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>After L4 S7 (beat image 2 of 2)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Lars tucking the envelope into a drawer, with a dreamy thought bubble of his lemonade stand by the front gate.</t>
         </is>
       </c>
-      <c r="K40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="K46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>completion</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>medal-skill1-silver.webp</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>MEDAL: silver</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>It's Mia's birthday!
+She's invited Lars to the gelato shop after school to celebrate.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l5-r4.webp</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>L5 opener, before L5 S1. Mia's first appearance.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Lars and his friend Mia walking together after school, Mia wearing a birthday badge.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n"/>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>word-drop</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>It's Mia's birthday, and the gelato shop has a birthday deal. Mia wants Lars to get one too. For Lars, his own gelato is a ______.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>lars-mia-sidebyside.webp</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>OPTIONS: 🍦 want | ✅ need | 🧾 bill
 CORRECT: 🍦 want</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-    </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>A birthday gelato costs $5. The only money Lars has is his $10 startup money. What should he do?</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>lars-deciding-512.webp</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🤝 Skip his own gelato and share Mia's.
 CHOICE B: 🍦 Buy his own, because the deal ends today.
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="80" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>true-false</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>True or false: the gelato is a need because the deal is only on today.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>CORRECT: False</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Nope! A deal that ends today doesn't turn a want into a need. Try again!</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="80" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>bucket-sort</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Sort each item into the right bucket. Is it a want or a need for Lars right now?</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>ITEMS:
 NEED: 🍋 Lemons for his stand
@@ -2384,86 +2645,124 @@
 WANT: 🍨 Extra gelato toppings</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>At the shop, the counter is a rainbow of flavors. Mia picks hers straight away.
+Lars looks at the cups and his tummy rumbles.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l5-r4.webp</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>After L5 S4</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Lars and Mia at a gelato counter full of colorful flavors, Mia pointing at hers.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>At the counter, a sign flashes: DEAL ENDS TODAY! Lars feels left out without his own cup. What should he do now?</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>lars-hands-on-hips-512.webp</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🤝 Stick with sharing Mia's gelato.
 CHOICE B: 🍦 Buy his own before the deal ends.
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>rank-order</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Look back at Lars's trip to the gelato shop. Put what he did in order, first to last.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>ITEMS: 🤔 First, Lars asks if it's a want or a need.
 ITEMS: 🤝 Then he asks Mia if they can share hers.
@@ -2471,200 +2770,238 @@
 ORDER: want, share, yes</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Mia is happy to share her gelato, and Lars doesn't have to pay. What happens to his $10 startup money?</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>lars-celebrating-512.webp</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🫙 It stays safe at $10
 CHOICE B: 🍦 It drops to $5
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Lars and Mia share the birthday gelato, one spoonful each.
 His startup envelope still holds $10.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>After L5 S7</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Lars and Mia leaving the gelato shop, sharing one gelato with two spoons, Mia in a birthday badge.</t>
         </is>
       </c>
-      <c r="K49" s="2" t="n"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="K57" s="2" t="n"/>
+    </row>
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>completion</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>medal-skill2-silver.webp</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>MEDAL: silver</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
-    </row>
-    <row r="51" ht="80" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>A week later, the movie everyone's talking about hits the cinema.
+Mia has an idea.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l6-r1.webp</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>L6 opener, before L6 S1</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Mia talking excitedly to Lars, a movie poster on the wall behind them.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Mia asks Lars to the movies. The ticket and popcorn cost $10, and Mom will pay half. Lars has saved $8 of pocket money. Can he pay his half?</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>lars-mia-chatting.webp</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: ✅ Yes, he has enough
 CHOICE B: ❌ No, he's short
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="64" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="80" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Earlier this week, Lars nearly bought a $5 mini dart blaster. What would have happened if he had bought it?</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 😬 He'd have $3, not enough for his $5 half.
 CHOICE B: 🎟️ The movie ticket would have been free.
@@ -2672,43 +3009,43 @@
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="80" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+    </row>
+    <row r="62" ht="112" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>bucket-sort</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Can Lars do it with his $8, without going below zero or borrowing? Sort each idea into Yes or No.</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Lars has $8, and his half of the movie costs $5. Which ideas work without going below zero or borrowing? Sort each idea into Yes or No.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>ITEMS:
 YES: 🎟️ Pay his $5 half
@@ -2717,43 +3054,43 @@
 NO: 🙋 Borrow $5 from Senna</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="112" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+    </row>
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>True or false? Check each statement against Lars's story.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>lars-deciding-512.webp</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>ROUNDS:
 Round 1 | Lars kept his money earlier this week. Now he can pay his half. | True | False | CORRECT: A
@@ -2761,43 +3098,43 @@
 Round 3 | Lars has to borrow from his brother Senna to go. | True | False | CORRECT: B</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+    </row>
+    <row r="64" ht="64" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Mom will pay half of the $10. Lars will pay his $5 from his $8. How much will he have left?</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>lars-hands-on-hips-512.webp</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 💵 $3
 CHOICE B: 🎟️ $5
@@ -2805,47 +3142,47 @@
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Not quite! $8 minus $5 leaves $3. Try again!</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="64" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="80" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>rank-order</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Look back at Lars's week. Put what happened in order, first to last.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>not allowed</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>ITEMS: 🎯 Earlier this week, Lars skips a $5 dart blaster.
 ITEMS: 📱 Today, Mia asks him to the movies.
@@ -2853,318 +3190,359 @@
 ORDER: blaster, asks, yes</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="80" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Friday night, Mom and Lars meet Mia at the cinema. The smell of popcorn hits them at the door.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l6-r1.webp</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>After L6 S6</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Lars, Mom and Mia arriving at a cinema entrance at night, a popcorn stand inside.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n"/>
+    </row>
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>drag-to-target</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>At the ticket counter, Mom pays her half. Drag Lars's $5 to the counter.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>lars-mia-sidebyside.webp</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>SOURCE: 💵 $5
 TARGET: 🎟️ Ticket counter
 SUCCESS: Paid his half, and $3 is still safe!</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-    </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+    </row>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Lars paid his own half. No borrowing, no stress.
 His startup money stayed at $10, and he still has $3 spare.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>beat-ex-m1-l6-r1.webp</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>After L6 S7 (beat image 1 of 2)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Lars and Mia waiting in line at the movie theater, tickets in hand, Lars looking relaxed.</t>
         </is>
       </c>
-      <c r="K58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="K68" s="2" t="n"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>While they wait, Mia doodles a lemon on her ticket.
 "I could design the sign for your stand," she says.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-lemon-ticket-r4.webp</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>After L6 S7 (beat image 2 of 2)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Close-up of Mia doodling a lemon on her movie ticket while Lars grins.</t>
         </is>
       </c>
-      <c r="K59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="K69" s="2" t="n"/>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>completion</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>medal-skill3-silver.webp</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>MEDAL: silver</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
+    </row>
+    <row r="71" ht="48" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>At the bus stop, Lars tells Mason his big news.
 Mom told the neighbors, and lots of them want to buy lemonade!</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>beat-ex-m1-l7-r1.webp</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>After L6 S8</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Lars and Mason at the school bus stop, Lars excitedly sharing his news, Mason listening.</t>
         </is>
       </c>
-      <c r="K61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="48" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="K71" s="2" t="n"/>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>word-drop</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Lars and Mia walk past a store with a slushie deal, on today only. Before reaching for his wallet, Lars ______.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>lars-mia-sidebyside.webp</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>OPTIONS: 🧠 stops and thinks | 🛍️ buys it straight away | 🙋 asks Mia to pay
 CORRECT: 🧠 stops and thinks</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="n"/>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+    </row>
+    <row r="73" ht="64" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Mia is designing Lars's sign. Today they buy the poster board and markers together. Lars's share is $6. Is paying his share a want or a need?</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: ✨ Want
 CHOICE B: ✅ Need
 CORRECT: B</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="64" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+    </row>
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>multiple-choice</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Paying his share comes before the slushie. Which skill is he using?</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>lars-hands-on-hips-512.webp</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🧠 Catch Impulse Spending
 CHOICE B: ✅ Choose Needs Over Wants
@@ -3172,421 +3550,12 @@
 CORRECT: B</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Lars has $8: his $3 spare plus this week's $5 pocket money. He pays his $6 share first. A slushie is $2. What should Lars do?</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>lars-deciding-512.webp</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>CHOICE A: 🥤 Buy his own slushie with his last $2
-CHOICE B: 🤝 Share one slushie with Mia
-CORRECT: B</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Hold up! His own slushie would use his last $2. Try again!</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>savings-goal</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Let's check the other choice. Drag his $6 share and a $2 slushie into the box to see what Lars would have left.</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>concept-wallet.webp</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>AVAILABLE: $8
-ITEMS: 🎨 Sign supplies ($6) 🥤 Slushie ($2)</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
-    </row>
-    <row r="67" ht="64" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>What if the slushie cost $3? After his share, Lars has $2. Can he buy his own?</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>lars-mia-chatting.webp</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>CHOICE A: ❌ No, he's $1 short
-CHOICE B: 🙋 Yes, if Mia lends him $1
-CORRECT: A</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
-    </row>
-    <row r="68" ht="48" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>drag-to-target</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Lars and Mia each pay $1 and share one slushie. Drag the slushie to Mia to share it.</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>lars-celebrating-512.webp</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>SOURCE: 🥤 Slushie
-TARGET: 🤝 Share with Mia
-SUCCESS: Shared! And Lars still has $1.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
-    </row>
-    <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>completion</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>MEDAL: none</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Image left blank: the live penny-fistpump.webp is retired art.</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
-    </row>
-    <row r="70" ht="48" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Scenario Beat</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Two straws, one slushie, and $1 still in Lars's pocket.
-"Deals like that used to get me every time," Lars laughs.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>prop-ex-m1-slushie-r2.webp</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>After L7 S8</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Lars and Mia sharing one slushie with two straws, Lars laughing.</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="n"/>
-    </row>
-    <row r="71" ht="64" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Scenario Beat</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Saturday morning. Lars looks at the note above his desk: 'Mountain bike'.
-His startup envelope stays at home. Today's money is just for the mall.</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>prop-ex-m1-bike-bubble-r1.webp</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>After L7 S8 (beat image 1 of 2)</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>Lars at his desk on a sunny morning, looking at a note on his wall that says 'Mountain bike'.</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="n"/>
-    </row>
-    <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Scenario Beat</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>But today he's going to the mall with his friends.
-What he does with his money today is up to you!</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>beat-ex-m1-l8-r2.webp</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>After L7 S8 (beat image 2 of 2)</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Lars heading out the front door with a small wallet, waving to Mom.</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="n"/>
-    </row>
-    <row r="73" ht="64" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>spotlight-rounds</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Lars has two weeks of pocket money, $10, at the mall. His startup money is safe at home. He sees a glow-in-the-dark yo-yo for $6. What do you want Lars to do?</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>lars-deciding-512.webp</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>CHOICE A: 🪀 Buy it. He wants it and will still have money left → SET cash=4 → GO Screen 1-buy
-CHOICE B: ✋ Don't buy it. He doesn't need it → SET cash=10 → GO Screen 1-keep</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="n"/>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>1-buy</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Lars buys the yo-yo for $6. He has {cash} left.</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>lars-walking-512.webp</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 2</t>
-        </is>
-      </c>
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="2" t="n"/>
     </row>
-    <row r="75" ht="16" customHeight="1">
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -3594,12 +3563,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>1-keep</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3609,25 +3578,31 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Lars puts the yo-yo back and keeps walking. He still has {cash}.</t>
+          <t>Lars has $8: his $3 spare plus this week's $5 pocket money. He pays his $6 share first. A slushie is $2. What should Lars do?</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>lars-hands-on-hips-512.webp</t>
+          <t>lars-deciding-512.webp</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CONTINUE → GO Screen 2</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n"/>
+          <t>CHOICE A: 🥤 Buy his own slushie with his last $2
+CHOICE B: 🤝 Share one slushie with Mia
+CORRECT: B</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Hold up! His own slushie would use his last $2. Try again!</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="n"/>
     </row>
-    <row r="76" ht="144" customHeight="1">
+    <row r="76" ht="64" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -3635,30 +3610,433 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>savings-goal</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Let's check the other choice. Drag his $6 share and a $2 slushie into the box to see what Lars would have left.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>concept-wallet.webp</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>AVAILABLE: $8
+ITEMS: 🎨 Sign supplies ($6) 🥤 Slushie ($2)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+    </row>
+    <row r="77" ht="48" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>What if the slushie cost $3? After his share, Lars has $2. Can he buy his own?</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>lars-mia-chatting.webp</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>CHOICE A: ❌ No, he's $1 short
+CHOICE B: 🙋 Yes, if Mia lends him $1
+CORRECT: A</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
+    </row>
+    <row r="78" ht="48" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>drag-to-target</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Lars and Mia each pay $1 and share one slushie. Drag the slushie to Mia to share it.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>lars-celebrating-512.webp</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>SOURCE: 🥤 Slushie
+TARGET: 🤝 Share with Mia
+SUCCESS: Shared! And Lars still has $1.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>completion</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>MEDAL: none</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Image left blank: the live penny-fistpump.webp is retired art.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n"/>
+    </row>
+    <row r="80" ht="64" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Two straws, one slushie, and $1 still in Lars's pocket.
+"Deals like that used to get me every time," Lars laughs.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-slushie-r2.webp</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>After L7 S8</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Lars and Mia sharing one slushie with two straws, Lars laughing.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n"/>
+    </row>
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Saturday morning. Lars looks at the note above his desk: 'Mountain bike'.
+His startup envelope stays at home. Today's money is just for the mall.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>prop-ex-m1-bike-bubble-r1.webp</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>After L7 S8 (beat image 1 of 2)</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Lars at his desk on a sunny morning, looking at a note on his wall that says 'Mountain bike'.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n"/>
+    </row>
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Beat</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>But today he's going to the mall with his friends.
+What he does with his money today is up to you!</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l8-r2.webp</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>After L7 S8 (beat image 2 of 2)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Lars heading out the front door with a small wallet, waving to Mom.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n"/>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Lars has two weeks of pocket money, $10, at the mall. His startup money is safe at home. He sees a glow-in-the-dark yo-yo for $6. What do you want Lars to do?</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>lars-deciding-512.webp</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>CHOICE A: 🪀 Buy it. He wants it and will still have money left → SET cash=4 → GO Screen 1-buy
+CHOICE B: ✋ Don't buy it. He doesn't need it → SET cash=10 → GO Screen 1-keep</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>1-buy</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Lars buys the yo-yo for $6. He has {cash} left.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>lars-walking-512.webp</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 2</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+    </row>
+    <row r="85" ht="144" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>1-keep</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Lars puts the yo-yo back and keeps walking. He still has {cash}.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>lars-hands-on-hips-512.webp</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 2</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>spotlight-rounds</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Lars has {cash} left when he passes the arcade. A game card costs $5. What do you want Lars to do?</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>IF cash &gt;= 5 THEN
 CHOICE A: 🕹️ Pay $5 and play → SET cash=cash-5 → GO Screen 2-played
@@ -3669,429 +4047,12 @@
 CHOICE B: 🚶 Skip the arcade → GO Screen 2-short</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="n"/>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>2-played</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Lars pays $5 and plays with his friends. He has {cash} left.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>lars-celebrating-512.webp</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 3</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>2-kept</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Lars skips the arcade, chats with his friends instead and keeps his {cash}.</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>lars-hands-on-hips-512.webp</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 3</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>2-short</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Lars can't pay the $5, so he skips it and keeps his {cash}.</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>lars-sitting-512.webp</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 3</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>2-alt</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>If Lars hadn't bought the yo-yo, he'd still have $10. He could pay for the card.</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>lars-thinking-512.webp</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 3</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="n"/>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>spotlight-rounds</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Meanwhile, across town, Mia has $10. Her friends invite her to a skate park session that costs $5. What do you want Mia to do?</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>mia-thinking.webp</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>CHOICE A: 🛹 Yes, Mia joins in ($5) → GO Screen 4
-CHOICE B: 💰 No, she doesn't want to spend the money → GO Screen 4-alt</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Melvin: Mia's art files in the repo are capitalized (Mia-*.webp). Rename them or confirm the lowercase names used here. Any skate park art should show Mia with her helmet on.</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="n"/>
-      <c r="K81" s="2" t="n"/>
-    </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Mia has $5 left after a fun afternoon at the skate park. When the group goes for a snack, she's glad she said yes.</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>mia-celebrating.webp</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 5</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n"/>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>4-alt</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>The next day, everyone is talking about the skate park, and the snack after. Mia still has her $10, but she missed all of it.</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>mia-walking.webp</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 5</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
-    </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>spotlight-rounds</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Later that afternoon, Lars has {cash}. He sees a cool water bottle for $4. What do you want Lars to do?</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>lars-deciding-512.webp</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>IF cash &gt;= 4 THEN
-CHOICE A: 🧴 Buy the water bottle ($4) → SET cash=cash-4 → GO Screen 5-buy
-CHOICE B: 💰 Don't buy the water bottle → GO Screen 5-save</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>5-buy</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Lars buys the water bottle and fills it straight away. He has {cash} left.</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>lars-walking-512.webp</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 6</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="n"/>
-    </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>5-save</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>binary-choice</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Lars skips the water bottle for now. He still has {cash}.</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>lars-hands-on-hips-512.webp</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>CONTINUE → GO Screen 6</t>
-        </is>
-      </c>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
       <c r="J86" s="2" t="n"/>
       <c r="K86" s="2" t="n"/>
     </row>
-    <row r="87" ht="112" customHeight="1">
+    <row r="87" ht="16" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -4104,25 +4065,442 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>2-played</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Lars pays $5 and plays with his friends. He has {cash} left.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>lars-celebrating-512.webp</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 3</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>2-kept</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Lars skips the arcade, chats with his friends instead and keeps his {cash}.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>lars-hands-on-hips-512.webp</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 3</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>2-short</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Lars can't pay the $5, so he skips it and keeps his {cash}.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>lars-sitting-512.webp</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 3</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>2-alt</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>If Lars hadn't bought the yo-yo, he'd still have $10. He could pay for the card.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>lars-thinking-512.webp</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 3</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="n"/>
+      <c r="K90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>spotlight-rounds</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Meanwhile, across town, Mia has $10. Her friends invite her to a skate park session that costs $5. What do you want Mia to do?</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>mia-thinking.webp</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>CHOICE A: 🛹 Yes, Mia joins in ($5) → GO Screen 4
+CHOICE B: 💰 No, she doesn't want to spend the money → GO Screen 4-alt</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Melvin: Mia's art files in the repo are capitalized (Mia-*.webp). Rename them or confirm the lowercase names used here. Any skate park art should show Mia with her helmet on.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n"/>
+      <c r="K91" s="2" t="n"/>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Mia has $5 left after a fun afternoon at the skate park. When the group goes for a snack, she's glad she said yes.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>mia-celebrating.webp</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 5</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="n"/>
+    </row>
+    <row r="93" ht="64" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>4-alt</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>The next day, everyone is talking about the skate park, and the snack after. Mia still has her $10, but she missed all of it.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>mia-walking.webp</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 5</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>spotlight-rounds</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Later that afternoon, Lars has {cash}. He sees a cool water bottle for $4. What do you want Lars to do?</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>lars-deciding-512.webp</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>IF cash &gt;= 4 THEN
+CHOICE A: 🧴 Buy the water bottle ($4) → SET cash=cash-4 → GO Screen 5-buy
+CHOICE B: 💰 Don't buy the water bottle → GO Screen 5-save</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>5-buy</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Lars buys the water bottle and fills it straight away. He has {cash} left.</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>lars-walking-512.webp</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 6</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="n"/>
+    </row>
+    <row r="96" ht="112" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>5-save</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>binary-choice</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Lars skips the water bottle for now. He still has {cash}.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>lars-hands-on-hips-512.webp</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUE → GO Screen 6</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="n"/>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>spotlight-rounds</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Then Mason messages: some friends are going bowling tonight. A game is $5. Lars has {cash}. What do you want Lars to do?</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>lars-mason-chatting.webp</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>IF cash &gt;= 5 THEN
 CHOICE A: 🎳 Go bowling ($5) → SET cash=cash-5 → GO Screen 7
@@ -4132,240 +4510,240 @@
 CHOICE B: 🚶 Skip bowling → GO Screen 7-skip</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
-      <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="n"/>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="2" t="n"/>
+      <c r="K97" s="2" t="n"/>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Lars bowls with the whole group. He has {cash} left.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>lars-celebrating-512.webp</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>CONTINUE → GO Screen 8</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="n"/>
-      <c r="J88" s="2" t="n"/>
-      <c r="K88" s="2" t="n"/>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="n"/>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>7-home</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Lars keeps his {cash}, but he misses bowling with his friends.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>lars-sitting-512.webp</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>CONTINUE → GO Screen 8</t>
         </is>
       </c>
-      <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="n"/>
-    </row>
-    <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="2" t="n"/>
+      <c r="K99" s="2" t="n"/>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>7-games</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>The group happily agrees, and Mason's mom makes popcorn. Lars joins in and still has {cash}.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>lars-mason-sidebyside.webp</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>CONTINUE → GO Screen 8</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
-      <c r="J90" s="2" t="n"/>
-      <c r="K90" s="2" t="n"/>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>7-skip</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Lars has {cash}, but he misses the night with his friends.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>lars-sitting-512.webp</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>CONTINUE → GO Screen 8</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="n"/>
-      <c r="J91" s="2" t="n"/>
-      <c r="K91" s="2" t="n"/>
-    </row>
-    <row r="92" ht="48" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n"/>
+      <c r="K101" s="2" t="n"/>
+    </row>
+    <row r="102" ht="80" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>completion</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>MEDAL: none</t>
         </is>
       </c>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="80" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
+    </row>
+    <row r="103" ht="48" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Tap a skill to test yourself. When all three are done, tap Finish.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>lars-waving-512.webp</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>HUB
 BUTTON: 🧠 Catch Impulse Spending → GO Screen 2
@@ -4374,383 +4752,383 @@
 BUTTON: Finish → GO Screen 8 WHEN complete</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n"/>
-      <c r="I93" s="2" t="n"/>
-      <c r="J93" s="2" t="n"/>
-      <c r="K93" s="2" t="n"/>
-    </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Catch Impulse Spending means pausing before you spend. Which one is a pause?</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 😴 Sleep on it first → GO Screen 3
 CHOICE B: ⏰ Buy before the timer ends → GO Screen 3
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="n"/>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="n"/>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="n"/>
+    </row>
+    <row r="105" ht="48" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>true-false</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>True or false: a flashing "only 1 minute left" deal is a good reason to buy straight away.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>lars-deciding-512.webp</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>CORRECT: False
 CONTINUE → GO Screen 1</t>
         </is>
       </c>
-      <c r="H95" s="2" t="n"/>
-      <c r="I95" s="2" t="n"/>
-      <c r="J95" s="2" t="n"/>
-      <c r="K95" s="2" t="n"/>
-    </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="2" t="n"/>
+      <c r="K105" s="2" t="n"/>
+    </row>
+    <row r="106" ht="64" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Choose Needs Over Wants means covering what you need before you spend on wants. Which one does Lars's stand need?</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>lars-hands-on-hips-512.webp</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 🍋 Lemons for his stand → GO Screen 5
 CHOICE B: 🍬 A big bag of candy → GO Screen 5
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="n"/>
-      <c r="J96" s="2" t="n"/>
-      <c r="K96" s="2" t="n"/>
-    </row>
-    <row r="97" ht="64" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
+    </row>
+    <row r="107" ht="48" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Lars's school shoes have a hole, and he needs new ones. He also wants a new game skin. Which should he buy first?</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>lars-walking-512.webp</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: 👟 School shoes → GO Screen 1
 CHOICE B: 🎮 Game skin → GO Screen 1
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="n"/>
-    </row>
-    <row r="98" ht="48" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
+    </row>
+    <row r="108" ht="48" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>binary-choice</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Don't Spend Money You Don't Have means never going below zero. Lars has $4. A comic costs $7. Can he buy it?</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>lars-sitting-512.webp</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>CHOICE A: ❌ No, he's $3 short → GO Screen 7
 CHOICE B: 🙋 Yes, if he borrows $3 → GO Screen 7
 CORRECT: A</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Hold up! Borrowing means spending money he doesn't have. Try again!</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
-    </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="n"/>
+    </row>
+    <row r="109" ht="64" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>word-drop</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Lars kept his $10 startup money safe, then earned $5 doing chores. Now he has $15, so he can ______ his whole stand kit!</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>lars-thinking-512.webp</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>OPTIONS: 💸 afford | 🙈 forget | 🗑️ lose
 CORRECT: 💸 afford
 CONTINUE → GO Screen 1</t>
         </is>
       </c>
-      <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="n"/>
-      <c r="J99" s="2" t="n"/>
-      <c r="K99" s="2" t="n"/>
-    </row>
-    <row r="100" ht="64" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="n"/>
+    </row>
+    <row r="110" ht="64" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>completion</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>MEDAL: gold</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>Image blank as live. Gold medals medal-skill1/2/3-gold.webp exist if Melvin wants them here.</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="n"/>
-    </row>
-    <row r="101" ht="64" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>With $15 in his envelope, Lars buys a jug, cups, lemons and sugar. Mia's sign goes on the front.
 On Saturday, his stand opens by the front gate.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>beat-ex-m1-l9-r1.webp</t>
         </is>
       </c>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="G111" s="2" t="n"/>
+      <c r="H111" s="2" t="n"/>
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>After L9 S8 (beat image 1 of 2)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>Lars at his new lemonade stand by the front gate, Mia's sign on the front, Mom watching from the porch.</t>
         </is>
       </c>
-      <c r="K101" s="2" t="n"/>
-    </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="K111" s="2" t="n"/>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Scenario Beat</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>He's one step closer to his mountain bike!</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>prop-ex-m1-lars-cheering-bike-r1.webp</t>
         </is>
       </c>
-      <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="n"/>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>After L9 S8 (beat image 2 of 2)</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>Lars behind his stand, proudly holding up a cup of lemonade.</t>
         </is>
       </c>
-      <c r="K102" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K102"/>

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -2837,7 +2837,11 @@
 His startup envelope still holds $10.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>beat-ex-m1-l5-r4.webp</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="inlineStr">

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1369,7 @@
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Senna loves his new phone case. That night, Lars tells Mom his big dream: swapping his old bike for a better mountain bike.
-Mom says she'll help, but Lars has to pay for part of it himself. Pocket money won't get him there, so Lars makes a plan: a lemonade stand!</t>
+His parents say they'll help, but Lars has to pay for part of it himself. Pocket money won't get him there, so Lars makes a plan.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>First he needs a jug, paper cups, lemons and sugar. That costs money too, so he decides to save for it.
+          <t>Lars wants to run a lemonade stand. First he needs a jug, paper cups, lemons, sugar and ingredients to bake cookies. That all costs money, so he decides to save for it.
 Mom agrees, as long as the stand goes by their front gate, where she can see him.</t>
         </is>
       </c>
@@ -1481,7 +1481,7 @@
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Saving for the stand sounds easy. But his friends keep heading to the corner store, and the weeks fly by.
+          <t>Saving for the lemonade stand idea sounds easy, but he keeps spending his money at the corner store. The weeks fly by.
 Then one afternoon, Lars borrows Senna's headphones...</t>
         </is>
       </c>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Over the next few weeks, Lars spends every dollar on fun stuff and forgets to save. Then he breaks Senna's headphones by accident. What's the real problem?</t>
+          <t>He accidentally breaks Senna's headphones. What's the problem Lars faces?</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Lars's friends are all buying a game skin before the timer runs out. Mason sees Lars holding off. What is Lars really doing by waiting?</t>
+          <t>Lars's friends are all buying the game skin before the timer runs out. Mason sees that Lars is holding off. What is Lars really doing by waiting?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Lars grabs an envelope to keep his stand money separate. He writes 'Startup money needed: $15' on the front.</t>
+          <t>Lars grabs an envelope to keep the money for his lemonade stand separate. He writes 'Startup money needed: $15' on the front.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>A birthday gelato costs $5. The only money Lars has is his $10 startup money. What should he do?</t>
+          <t>The gelato costs $5. The only money Lars has is his $10 startup money. What should he do?</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>CHOICE A: 🤝 Skip his own gelato and share Mia's.
+          <t>CHOICE A: 🤝 Skip his own gelato and ask if Mia wants to share.
 CHOICE B: 🍦 Buy his own, because the deal ends today.
 CORRECT: A</t>
         </is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>True or false: the gelato is a need because the deal is only on today.</t>
+          <t>True or false: the gelato is a 'Need' because the deal is only on today.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>At the counter, a sign flashes: DEAL ENDS TODAY! Lars feels left out without his own cup. What should he do now?</t>
+          <t>The birthday deal is only on today. Lars feels left out without his own cup. What should he do now?</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Earlier this week, Lars nearly bought a $5 mini dart blaster. What would have happened if he had bought it?</t>
+          <t>Earlier this week, Lars nearly bought a $5 mini dart blaster, but he decided he didn't need it. What would have happened if he had bought it?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Lars has $8, and his half of the movie costs $5. Which ideas work without going below zero or borrowing? Sort each idea into Yes or No.</t>
+          <t>Because he didn't buy the blaster, Lars has $8. His half of the movie costs $5. Which are good ideas for Lars? Sort each idea into Yes or No.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3053,8 +3053,8 @@
         <is>
           <t>ITEMS:
 YES: 🎟️ Pay his $5 half
-YES: 💰 Keep $3 for later
-NO: 🎯 Dart blaster and the movie
+YES: 💰 Save the remaining $3 for later
+NO: 🎯 Buy the dart blaster and movie ticket
 NO: 🙋 Borrow $5 from Senna</t>
         </is>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Mom will pay half of the $10. Lars will pay his $5 from his $8. How much will he have left?</t>
+          <t>Lars's parents will pay half of the $10. Lars pays the other half from the $8 he has. How much will Lars have left?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3407,8 +3407,8 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>At the bus stop, Lars tells Mason his big news.
-Mom told the neighbors, and lots of them want to buy lemonade!</t>
+          <t>At the bus stop, Lars shares some big news with Mason.
+Mom told the neighbors about his lemonade stand idea, and lots of them want to buy some!</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3824,8 +3824,8 @@
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Saturday morning. Lars looks at the note above his desk: 'Mountain bike'.
-His startup envelope stays at home. Today's money is just for the mall.</t>
+          <t>Saturday morning. Lars and his friends are going to the mall. Lars looks at the note and picture above his desk: 'Mountain bike'.
+He decides to leave the money for his startup at home.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3862,8 +3862,8 @@
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>But today he's going to the mall with his friends.
-What he does with his money today is up to you!</t>
+          <t>Lars has two weeks of pocket money, $10, at the mall. And what he does with the money he brought, is up to you!
+Let's see the choices Lars has to make today.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5075,7 +5075,8 @@
       <c r="E111" s="2" t="inlineStr">
         <is>
           <t>With $15 in his envelope, Lars buys a jug, cups, lemons and sugar. Mia's sign goes on the front.
-On Saturday, his stand opens by the front gate.</t>
+On Saturday, his stand opens by the front gate.
+He's one step closer to his mountain bike!</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5096,43 +5097,6 @@
         </is>
       </c>
       <c r="K111" s="2" t="n"/>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Scenario Beat</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>He's one step closer to his mountain bike!</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>prop-ex-m1-lars-cheering-bike-r1.webp</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>After L9 S8 (beat image 2 of 2)</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>Lars behind his stand, proudly holding up a cup of lemonade.</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K102"/>

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -741,7 +741,7 @@
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Lars's birthday money is gone. At home, he watches his big brother Senna count his money.
+          <t>Lars spent all his birthday money. At home, he watches his big brother Senna count his bills and coins.
 Senna earned it walking dogs in the neighborhood. "It's a great way to make some money," Senna says.</t>
         </is>
       </c>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Next day, Lars gets his $5 pocket money. Then his tablet flashes: 💥 RARE SKIN DEAL! ONLY 1 MINUTE LEFT! 💥 Why is the game rushing him?</t>
+          <t>The next day, Lars gets his $5 pocket money. Then his tablet flashes: 💥 RARE SKIN DEAL! ONLY 1 MINUTE LEFT! 💥 Why is the game rushing him?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>At lunch, everyone's phones are buzzing. A new skin has dropped, and a countdown is ticking.
+          <t>One afternoon, Lars's friends all ping him. A new skin has dropped on their favorite game. A limited time offer and the countdown is ticking.
 Lars remembers Mason's words. His startup money is still $0.</t>
         </is>
       </c>
@@ -2833,7 +2833,7 @@
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Lars and Mia share the birthday gelato, one spoonful each.
+          <t>Lars and Mia share the birthday gelato. She's happy Lars came along, and Lars is grateful for Mia's generosity. He decides to repay the favor to Mia when he can.
 His startup envelope still holds $10.</t>
         </is>
       </c>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Lars has two weeks of pocket money, $10, at the mall. His startup money is safe at home. He sees a glow-in-the-dark yo-yo for $6. What do you want Lars to do?</t>
+          <t>Lars sees a glow-in-the-dark yo-yo for $6. What do you want Lars to do?</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">

--- a/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
+++ b/lib/academy/lessons/payload/source/explorer-m1/workbook.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>em1-03-l1r11-lars-lemonade-r3.webp</t>
+          <t>prop-ex-m1-stand-set-lars-r1.webp</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
